--- a/src/nodes/HPC/compressor_stage_4_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_4_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.6726261413310661</v>
+        <v>4.6428951729378527</v>
       </c>
       <c r="B1">
-        <v>8.2772525238292474</v>
+        <v>8.2939658073203137</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.0826470580104424</v>
+        <v>4.053579521748965</v>
       </c>
       <c r="B2">
-        <v>8.0934210819263761</v>
+        <v>8.1080185539075487</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.5579619451871647</v>
+        <v>3.5297514286771081</v>
       </c>
       <c r="B3">
-        <v>7.8555221315685309</v>
+        <v>7.8682384314861054</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3.0509179313173491</v>
+        <v>3.0236167379847263</v>
       </c>
       <c r="B4">
-        <v>7.6030152433022353</v>
+        <v>7.6139137659483955</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.558640354036644</v>
+        <v>2.532292264329921</v>
       </c>
       <c r="B5">
-        <v>7.3382808181125423</v>
+        <v>7.347414627935331</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2.0798361370608269</v>
+        <v>2.0544810976355787</v>
       </c>
       <c r="B6">
-        <v>7.0623896043763343</v>
+        <v>7.0698071190439924</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.6136982646176739</v>
+        <v>1.5893738294389825</v>
       </c>
       <c r="B7">
-        <v>6.776009861838812</v>
+        <v>6.7817565989396407</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.1596839157359509</v>
+        <v>1.1364260293795654</v>
       </c>
       <c r="B8">
-        <v>6.4795910803568235</v>
+        <v>6.483710606805718</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.71707144687093061</v>
+        <v>0.69491391433899008</v>
       </c>
       <c r="B9">
-        <v>6.1737308261092805</v>
+        <v>6.1762641155335647</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.28510534236783713</v>
+        <v>0.264079728662736</v>
       </c>
       <c r="B10">
-        <v>5.8590547135096021</v>
+        <v>5.8600400245267252</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.13692657929481991</v>
+        <v>-0.15679082069070069</v>
       </c>
       <c r="B11">
-        <v>5.5361524735871788</v>
+        <v>5.5356255055296106</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.5494545517391739</v>
+        <v>-0.56812924292682332</v>
       </c>
       <c r="B12">
-        <v>5.2053803668025926</v>
+        <v>5.2033752729216243</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.95182435112322938</v>
+        <v>-0.96927937452014834</v>
       </c>
       <c r="B13">
-        <v>4.8661966547251838</v>
+        <v>4.8627499392812243</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.3436765612289692</v>
+        <v>-1.3598807336331305</v>
       </c>
       <c r="B14">
-        <v>4.5183037181527776</v>
+        <v>4.5134531769990414</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.7269154537984439</v>
+        <v>-1.7418432379109716</v>
       </c>
       <c r="B15">
-        <v>4.1632784136883556</v>
+        <v>4.1570549995152977</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.1032868873860711</v>
+        <v>-2.1169179221379806</v>
       </c>
       <c r="B16">
-        <v>3.802566421866175</v>
+        <v>3.7949948134727838</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.4716393798356981</v>
+        <v>-2.483949890172179</v>
       </c>
       <c r="B17">
-        <v>3.4352142431404191</v>
+        <v>3.42632325727492</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.8304609123730713</v>
+        <v>-2.8414226403121288</v>
       </c>
       <c r="B18">
-        <v>3.059969831001462</v>
+        <v>3.0497937179803754</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.1796946604621166</v>
+        <v>-3.1892791795448416</v>
       </c>
       <c r="B19">
-        <v>2.6767861311644885</v>
+        <v>2.6653593455081483</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.5196475981263107</v>
+        <v>-3.5278273920294461</v>
       </c>
       <c r="B20">
-        <v>2.2859173374008832</v>
+        <v>2.2732732304923138</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.8506266993891232</v>
+        <v>-3.8573751619250678</v>
       </c>
       <c r="B21">
-        <v>1.8876176434820338</v>
+        <v>1.8737884635669517</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.1728812074893371</v>
+        <v>-4.1781724714423234</v>
       </c>
       <c r="B22">
-        <v>1.4820934384637374</v>
+        <v>1.4671105381110434</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.4864294425269646</v>
+        <v>-4.4902376949977993</v>
       </c>
       <c r="B23">
-        <v>1.0693598925394265</v>
+        <v>1.05325455848318</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.7912319938173287</v>
+        <v>-4.7935313050595694</v>
       </c>
       <c r="B24">
-        <v>0.64938437118694081</v>
+        <v>0.63218803178685667</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.0872494506757526</v>
+        <v>-5.08801377409571</v>
       </c>
       <c r="B25">
-        <v>0.22213423988412095</v>
+        <v>0.203878465125565</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.3744271550411735</v>
+        <v>-5.3736302819915487</v>
       </c>
       <c r="B26">
-        <v>-0.2124357616764645</v>
+        <v>-0.23171920538972479</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-5.6526494593470238</v>
+        <v>-5.6502648383014256</v>
       </c>
       <c r="B27">
-        <v>-0.65442139694335544</v>
+        <v>-0.67470032761817034</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-5.9217854686503522</v>
+        <v>-5.9177861599969281</v>
       </c>
       <c r="B28">
-        <v>-1.1039310551503634</v>
+        <v>-1.1251728204114504</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.1817042880082038</v>
+        <v>-6.1760629640496507</v>
       </c>
       <c r="B29">
-        <v>-1.5610731255313002</v>
+        <v>-1.5832446026212486</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.4323050931439116</v>
+        <v>-6.4249941272528428</v>
       </c>
       <c r="B30">
-        <v>-2.025931096919662</v>
+        <v>-2.0489988007604323</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-6.6736073424459486</v>
+        <v>-6.6645991656864165</v>
       </c>
       <c r="B31">
-        <v>-2.4984888565476804</v>
+        <v>-2.52241937198661</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-6.9056605649690725</v>
+        <v>-6.894927755251949</v>
       </c>
       <c r="B32">
-        <v>-2.9787053912472765</v>
+        <v>-3.0034654811185804</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.1285142897680354</v>
+        <v>-7.116029571851012</v>
       </c>
       <c r="B33">
-        <v>-3.4665396878503665</v>
+        <v>-3.4920962929751362</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.3421463113436234</v>
+        <v>-7.3278823441481462</v>
       </c>
       <c r="B34">
-        <v>-3.9620101339049465</v>
+        <v>-3.9883301153069239</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-7.5462474859807385</v>
+        <v>-7.530176011859762</v>
       </c>
       <c r="B35">
-        <v>-4.4653727198233444</v>
+        <v>-4.49242182759199</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-7.7404369354103046</v>
+        <v>-7.7225285674652353</v>
       </c>
       <c r="B36">
-        <v>-4.9769428367339632</v>
+        <v>-5.0046854522402224</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-7.9243337813632557</v>
+        <v>-7.9045580034439453</v>
       </c>
       <c r="B37">
-        <v>-5.497035875765218</v>
+        <v>-5.5254350116615258</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.0973944656140375</v>
+        <v>-8.0757191499951464</v>
       </c>
       <c r="B38">
-        <v>-6.02610193726683</v>
+        <v>-6.0551186528828254</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.2584247101111679</v>
+        <v>-8.2348141881976051</v>
       </c>
       <c r="B39">
-        <v>-6.5651299584738014</v>
+        <v>-6.5947210213991863</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-8.40606755684669</v>
+        <v>-8.38048213684997</v>
       </c>
       <c r="B40">
-        <v>-7.1152435858424559</v>
+        <v>-7.1453608873227132</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-8.5389660478126377</v>
+        <v>-8.51136201475088</v>
       </c>
       <c r="B41">
-        <v>-7.6775664658291065</v>
+        <v>-7.7081570207654986</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-8.5389660478126377</v>
+        <v>-8.51136201475088</v>
       </c>
       <c r="B42">
-        <v>-7.6775664658291065</v>
+        <v>-7.7081570207654986</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-8.3535497472865554</v>
+        <v>-8.327808619225733</v>
       </c>
       <c r="B43">
-        <v>-7.1587316306159714</v>
+        <v>-7.1886602048728436</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.1624086094314041</v>
+        <v>-8.1385134130181864</v>
       </c>
       <c r="B44">
-        <v>-6.6446373202680693</v>
+        <v>-6.6738833411546965</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-7.9646768267042365</v>
+        <v>-7.9426080215853085</v>
       </c>
       <c r="B45">
-        <v>-6.1360004778092723</v>
+        <v>-6.16454026128176</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-7.7594885915621061</v>
+        <v>-7.7392240703841635</v>
       </c>
       <c r="B46">
-        <v>-5.6335380462634506</v>
+        <v>-5.661344796924725</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-7.5461160950411212</v>
+        <v>-7.5276315925976371</v>
       </c>
       <c r="B47">
-        <v>-5.1378526971638072</v>
+        <v>-5.1648970041732714</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.324383522493644</v>
+        <v>-7.3076542523118988</v>
       </c>
       <c r="B48">
-        <v>-4.6490900160808888</v>
+        <v>-4.6753418367930282</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.0942530578510885</v>
+        <v>-7.0792541213389377</v>
       </c>
       <c r="B49">
-        <v>-4.1672813170945666</v>
+        <v>-4.1927104729686029</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-6.8556868850448769</v>
+        <v>-6.8423932714907441</v>
       </c>
       <c r="B50">
-        <v>-3.6924579142847236</v>
+        <v>-3.7170340908846136</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-6.6086980163778195</v>
+        <v>-6.5970847536498125</v>
       </c>
       <c r="B51">
-        <v>-3.2246090326473733</v>
+        <v>-3.2483019622978935</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.3535027776382966</v>
+        <v>-6.3435455349806578</v>
       </c>
       <c r="B52">
-        <v>-2.7635555408430803</v>
+        <v>-2.7863357332541594</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.0903683229860794</v>
+        <v>-6.0820435617183009</v>
       </c>
       <c r="B53">
-        <v>-2.3090762184485509</v>
+        <v>-2.3309151433713522</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-5.8195618065809382</v>
+        <v>-5.8128467800977592</v>
       </c>
       <c r="B54">
-        <v>-1.8609498450404836</v>
+        <v>-1.8818199322674072</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.5413044983379081</v>
+        <v>-5.5361771160688535</v>
       </c>
       <c r="B55">
-        <v>-1.4189931952320509</v>
+        <v>-1.43886766970779</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.2556341311930712</v>
+        <v>-5.2520724144406277</v>
       </c>
       <c r="B56">
-        <v>-0.98317502378230226</v>
+        <v>-1.0020272460480708</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-4.9625425538377792</v>
+        <v>-4.960524499736918</v>
       </c>
       <c r="B57">
-        <v>-0.55350208048675786</v>
+        <v>-0.57130538179134616</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.6620216149633773</v>
+        <v>-4.6615251964815672</v>
       </c>
       <c r="B58">
-        <v>-0.12998111514093708</v>
+        <v>-0.14670879744071474</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.3540646385327255</v>
+        <v>-4.3550678088439057</v>
       </c>
       <c r="B59">
-        <v>0.28738234407711455</v>
+        <v>0.27175700281668708</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.0386708495947481</v>
+        <v>-4.0411515595752361</v>
       </c>
       <c r="B60">
-        <v>0.69858765545922885</v>
+        <v>0.68409138005754244</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.7158409484698822</v>
+        <v>-3.7197771510723445</v>
       </c>
       <c r="B61">
-        <v>1.1036353989147132</v>
+        <v>1.0902949116744993</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.3855756354785611</v>
+        <v>-3.3909452857320215</v>
       </c>
       <c r="B62">
-        <v>1.5025261543528727</v>
+        <v>1.4903681750602005</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.0479196818613561</v>
+        <v>-3.0547008675353928</v>
       </c>
       <c r="B63">
-        <v>1.895296995172822</v>
+        <v>1.8843480827244934</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.703094142539364</v>
+        <v>-2.7112656068009171</v>
       </c>
       <c r="B64">
-        <v>2.2821309687329081</v>
+        <v>2.2724168876460307</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.3513641433538188</v>
+        <v>-2.3609054154313904</v>
       </c>
       <c r="B65">
-        <v>2.6632476158812843</v>
+        <v>2.6547931779206668</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.9929948101459474</v>
+        <v>-2.0038862053296049</v>
       </c>
       <c r="B66">
-        <v>3.0388664774661076</v>
+        <v>3.0316955416442584</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.6278761299535536</v>
+        <v>-1.6400976373600984</v>
       </c>
       <c r="B67">
-        <v>3.408896455845154</v>
+        <v>3.403033276515532</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.2543975346007217</v>
+        <v>-1.2679243682343819</v>
       </c>
       <c r="B68">
-        <v>3.7720038994146758</v>
+        <v>3.7674785186447086</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.87129209481492786</v>
+        <v>-0.88609571240932483</v>
       </c>
       <c r="B69">
-        <v>4.1271397111656825</v>
+        <v>4.123986723841087</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.48016799215094919</v>
+        <v>-0.49622461947627539</v>
       </c>
       <c r="B70">
-        <v>4.4756355664297178</v>
+        <v>4.47388378829877</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.082777798886018134</v>
+        <v>-0.10006885784762196</v>
       </c>
       <c r="B71">
-        <v>4.8189427051251954</v>
+        <v>4.8186146539183676</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.32142346064008548</v>
+        <v>0.30291816391454873</v>
       </c>
       <c r="B72">
-        <v>5.1566098531774589</v>
+        <v>5.15773000504169</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.73329282110125549</v>
+        <v>0.71359602147376666</v>
       </c>
       <c r="B73">
-        <v>5.48792733204921</v>
+        <v>5.4905232429585631</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.1526380052886038</v>
+        <v>1.1317718675457329</v>
       </c>
       <c r="B74">
-        <v>5.8130543593456574</v>
+        <v>5.817152894309662</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.579003548332055</v>
+        <v>1.5569888868698312</v>
       </c>
       <c r="B75">
-        <v>6.1323680885853626</v>
+        <v>6.137994475861734</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.011930546599547</v>
+        <v>1.9887868152280046</v>
       </c>
       <c r="B76">
-        <v>6.4462485207977851</v>
+        <v>6.45342633953493</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.451016101787459</v>
+        <v>2.4267615597787167</v>
       </c>
       <c r="B77">
-        <v>6.7550292810829378</v>
+        <v>6.7637806625798875</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.8960847756679184</v>
+        <v>2.8707371621439361</v>
       </c>
       <c r="B78">
-        <v>7.0588556433121532</v>
+        <v>7.0692020884157145</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.3467202753856156</v>
+        <v>3.320296095217437</v>
       </c>
       <c r="B79">
-        <v>7.35807232411551</v>
+        <v>7.3700338376886467</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.8020706757289373</v>
+        <v>3.7745839079468206</v>
       </c>
       <c r="B80">
-        <v>7.6533847710746326</v>
+        <v>7.6669782965144684</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.25974554879565</v>
+        <v>4.2312030851407174</v>
       </c>
       <c r="B81">
-        <v>7.94677240862688</v>
+        <v>7.9620062991242033</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.6726261413310661</v>
+        <v>4.6428951729378527</v>
       </c>
       <c r="B82">
-        <v>8.2772525238292474</v>
+        <v>8.2939658073203137</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.7518629331670637</v>
+        <v>4.7370345459494159</v>
       </c>
       <c r="B1">
-        <v>9.3784925672511026</v>
+        <v>9.3859910441078682</v>
       </c>
       <c r="C1">
         <v>224.36768702792492</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.04304755249163</v>
+        <v>3.9945989515935967</v>
       </c>
       <c r="B2">
-        <v>9.1949869561410669</v>
+        <v>9.2268146512411224</v>
       </c>
       <c r="C2">
         <v>224.36768702792492</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.4511488680028384</v>
+        <v>3.3902989271565138</v>
       </c>
       <c r="B3">
-        <v>8.9234497747367154</v>
+        <v>8.9639717760877691</v>
       </c>
       <c r="C3">
         <v>224.36768702792492</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.8852407552049262</v>
+        <v>2.8149532248884106</v>
       </c>
       <c r="B4">
-        <v>8.63234318268854</v>
+        <v>8.67939957569243</v>
       </c>
       <c r="C4">
         <v>224.36768702792492</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.3400173874805024</v>
+        <v>2.2622415422675477</v>
       </c>
       <c r="B5">
-        <v>8.3256621632972454</v>
+        <v>8.3778412420497652</v>
       </c>
       <c r="C5">
         <v>224.36768702792492</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.8131805578679867</v>
+        <v>1.7294522117365487</v>
       </c>
       <c r="B6">
-        <v>8.0051371346663824</v>
+        <v>8.0613317979780721</v>
       </c>
       <c r="C6">
         <v>224.36768702792492</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.3033415388503047</v>
+        <v>1.2149606136728219</v>
       </c>
       <c r="B7">
-        <v>7.6718137290112507</v>
+        <v>7.731090470367481</v>
       </c>
       <c r="C7">
         <v>224.36768702792492</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.80960758306916281</v>
+        <v>0.71773540594814766</v>
       </c>
       <c r="B8">
-        <v>7.3263641339183092</v>
+        <v>7.38789124965745</v>
       </c>
       <c r="C8">
         <v>224.36768702792492</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.33072457078975803</v>
+        <v>0.23630564877136781</v>
       </c>
       <c r="B9">
-        <v>6.9697326296588384</v>
+        <v>7.03283803076726</v>
       </c>
       <c r="C9">
         <v>224.36768702792492</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.13463520102522741</v>
+        <v>-0.23089047831080903</v>
       </c>
       <c r="B10">
-        <v>6.6029189005129378</v>
+        <v>6.667102911748489</v>
       </c>
       <c r="C10">
         <v>224.36768702792492</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.58773239624664275</v>
+        <v>-0.68533872073728042</v>
       </c>
       <c r="B11">
-        <v>6.226872154111204</v>
+        <v>6.2918008987021352</v>
       </c>
       <c r="C11">
         <v>224.36768702792492</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.0292958821851872</v>
+        <v>-1.1278880117124797</v>
       </c>
       <c r="B12">
-        <v>5.8421411857582406</v>
+        <v>5.9075690897995932</v>
       </c>
       <c r="C12">
         <v>224.36768702792492</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.4579943790774121</v>
+        <v>-1.5569161105173788</v>
       </c>
       <c r="B13">
-        <v>5.4477236181041926</v>
+        <v>5.513190043444447</v>
       </c>
       <c r="C13">
         <v>224.36768702792492</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.8730672674303277</v>
+        <v>-1.9714883189503674</v>
       </c>
       <c r="B14">
-        <v>5.0430467482713</v>
+        <v>5.1079622974816745</v>
       </c>
       <c r="C14">
         <v>224.36768702792492</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.2780967159069458</v>
+        <v>-2.3758912828029537</v>
       </c>
       <c r="B15">
-        <v>4.6308077439246516</v>
+        <v>4.6951028472896228</v>
       </c>
       <c r="C15">
         <v>224.36768702792492</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.6763674628704117</v>
+        <v>-2.7740558825794275</v>
       </c>
       <c r="B16">
-        <v>4.2134798247629357</v>
+        <v>4.2775616973776964</v>
       </c>
       <c r="C16">
         <v>224.36768702792492</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.065631737328439</v>
+        <v>-3.16326859364211</v>
       </c>
       <c r="B17">
-        <v>3.7893705480763624</v>
+        <v>3.8533024312461284</v>
       </c>
       <c r="C17">
         <v>224.36768702792492</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.4429588926498411</v>
+        <v>-3.5399973671977429</v>
       </c>
       <c r="B18">
-        <v>3.3562733049430653</v>
+        <v>3.4196743552764963</v>
       </c>
       <c r="C18">
         <v>224.36768702792492</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.8082192890032664</v>
+        <v>-3.9040804629727588</v>
       </c>
       <c r="B19">
-        <v>2.9140904840012909</v>
+        <v>2.9765560883848758</v>
       </c>
       <c r="C19">
         <v>224.36768702792492</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.1619835382573278</v>
+        <v>-4.2561987178235148</v>
       </c>
       <c r="B20">
-        <v>2.4632517232793161</v>
+        <v>2.5244585776209738</v>
       </c>
       <c r="C20">
         <v>224.36768702792492</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.5048222522806363</v>
+        <v>-4.5970329686063645</v>
       </c>
       <c r="B21">
-        <v>2.0041866608054191</v>
+        <v>2.0638927700344958</v>
       </c>
       <c r="C21">
         <v>224.36768702792492</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.8372010124285607</v>
+        <v>-4.9271394036426344</v>
       </c>
       <c r="B22">
-        <v>1.5372458526519996</v>
+        <v>1.595276067796328</v>
       </c>
       <c r="C22">
         <v>224.36768702792492</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.1591652780035231</v>
+        <v>-5.2465756171135327</v>
       </c>
       <c r="B23">
-        <v>1.0624635270679439</v>
+        <v>1.1186516935620794</v>
       </c>
       <c r="C23">
         <v>224.36768702792492</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.4706554777946952</v>
+        <v>-5.5552745546652371</v>
       </c>
       <c r="B24">
-        <v>0.57979483034626422</v>
+        <v>0.63396932510854231</v>
       </c>
       <c r="C24">
         <v>224.36768702792492</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.7716120405912568</v>
+        <v>-5.8531691619439306</v>
       </c>
       <c r="B25">
-        <v>0.089194908779966553</v>
+        <v>0.1411786402125059</v>
       </c>
       <c r="C25">
         <v>224.36768702792492</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.0619516653033747</v>
+        <v>-6.1401654244262573</v>
       </c>
       <c r="B26">
-        <v>-0.40939895857657627</v>
+        <v>-0.359790916124461</v>
       </c>
       <c r="C26">
         <v>224.36768702792492</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.3414961313251839</v>
+        <v>-6.4160614869107642</v>
       </c>
       <c r="B27">
-        <v>-0.91612096162357226</v>
+        <v>-0.86909083000170051</v>
       </c>
       <c r="C27">
         <v>224.36768702792492</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.6100434881718089</v>
+        <v>-6.6806285340264591</v>
       </c>
       <c r="B28">
-        <v>-1.4311231574998651</v>
+        <v>-1.386892820293774</v>
       </c>
       <c r="C28">
         <v>224.36768702792492</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.8673917853583744</v>
+        <v>-6.9336377504023545</v>
       </c>
       <c r="B29">
-        <v>-1.9545576033442973</v>
+        <v>-1.9133686058752435</v>
       </c>
       <c r="C29">
         <v>224.36768702792492</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.1134028357856156</v>
+        <v>-7.1749387038296248</v>
       </c>
       <c r="B30">
-        <v>-2.4865283461214087</v>
+        <v>-2.4486310814764081</v>
       </c>
       <c r="C30">
         <v>224.36768702792492</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.3481935058967265</v>
+        <v>-7.40469449474811</v>
       </c>
       <c r="B31">
-        <v>-3.0269473920985308</v>
+        <v>-2.992557845250539</v>
       </c>
       <c r="C31">
         <v>224.36768702792492</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.5719444255205151</v>
+        <v>-7.6231466067598221</v>
       </c>
       <c r="B32">
-        <v>-3.5756787373686945</v>
+        <v>-3.544967671206646</v>
       </c>
       <c r="C32">
         <v>224.36768702792492</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.7848362244857841</v>
+        <v>-7.83053652346676</v>
       </c>
       <c r="B33">
-        <v>-4.1325863780249241</v>
+        <v>-4.1056793333537334</v>
       </c>
       <c r="C33">
         <v>224.36768702792492</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.9869206405072131</v>
+        <v>-8.02695321457505</v>
       </c>
       <c r="B34">
-        <v>-4.6976313585337888</v>
+        <v>-4.6746260626730054</v>
       </c>
       <c r="C34">
         <v>224.36768702792492</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.1777338428429829</v>
+        <v>-8.2118755942073083</v>
       </c>
       <c r="B35">
-        <v>-5.2711629168560368</v>
+        <v>-5.2521989180344573</v>
       </c>
       <c r="C35">
         <v>224.36768702792492</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.356683108637144</v>
+        <v>-8.3846300625902668</v>
       </c>
       <c r="B36">
-        <v>-5.8536273393259526</v>
+        <v>-5.838903415280269</v>
       </c>
       <c r="C36">
         <v>224.36768702792492</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.52317571503375</v>
+        <v>-8.54454301995066</v>
       </c>
       <c r="B37">
-        <v>-6.4454709122778322</v>
+        <v>-6.4352450702526349</v>
       </c>
       <c r="C37">
         <v>224.36768702792492</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.6763176593241926</v>
+        <v>-8.6905816540694119</v>
       </c>
       <c r="B38">
-        <v>-7.0473667685049648</v>
+        <v>-7.0419989766488369</v>
       </c>
       <c r="C38">
         <v>224.36768702792492</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.8140098193892076</v>
+        <v>-8.8202763029441869</v>
       </c>
       <c r="B39">
-        <v>-7.6608954266366345</v>
+        <v>-7.6610185395865322</v>
       </c>
       <c r="C39">
         <v>224.36768702792492</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-8.9338517932568688</v>
+        <v>-8.9307980921268477</v>
       </c>
       <c r="B40">
-        <v>-8.28786425176114</v>
+        <v>-8.2944267420384818</v>
       </c>
       <c r="C40">
         <v>224.36768702792492</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.03344317895526</v>
+        <v>-9.0193181471692458</v>
       </c>
       <c r="B41">
-        <v>-8.9300806089667653</v>
+        <v>-8.9443465669774351</v>
       </c>
       <c r="C41">
         <v>224.36768702792492</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.03344317895526</v>
+        <v>-9.0193181471692458</v>
       </c>
       <c r="B42">
-        <v>-8.9300806089667653</v>
+        <v>-8.9443465669774351</v>
       </c>
       <c r="C42">
         <v>224.36768702792492</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-8.8334091871692628</v>
+        <v>-8.8101236826639848</v>
       </c>
       <c r="B43">
-        <v>-8.3634917765436576</v>
+        <v>-8.3849891622636843</v>
       </c>
       <c r="C43">
         <v>224.36768702792492</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.6303748304317409</v>
+        <v>-8.5996523594571652</v>
       </c>
       <c r="B44">
-        <v>-7.7991620469412215</v>
+        <v>-7.8265900006009081</v>
       </c>
       <c r="C44">
         <v>224.36768702792492</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.4224893744519829</v>
+        <v>-8.3856256242028735</v>
       </c>
       <c r="B45">
-        <v>-7.2384849169920127</v>
+        <v>-7.2708590659578487</v>
       </c>
       <c r="C45">
         <v>224.36768702792492</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.20790208493928</v>
+        <v>-8.1657649235551943</v>
       </c>
       <c r="B46">
-        <v>-6.6828538835285789</v>
+        <v>-6.71950634230324</v>
       </c>
       <c r="C46">
         <v>224.36768702792492</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-7.9850360085907139</v>
+        <v>-7.9381233850597033</v>
       </c>
       <c r="B47">
-        <v>-6.1334563019934265</v>
+        <v>-6.1739928973326057</v>
       </c>
       <c r="C47">
         <v>224.36768702792492</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.753409316054543</v>
+        <v>-7.7020808598279329</v>
       </c>
       <c r="B48">
-        <v>-5.5906549622688537</v>
+        <v>-5.6347841336486164</v>
       </c>
       <c r="C48">
         <v>224.36768702792492</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.5128139589668139</v>
+        <v>-7.4573488798629057</v>
       </c>
       <c r="B49">
-        <v>-5.0546065128470978</v>
+        <v>-5.1020965375807252</v>
       </c>
       <c r="C49">
         <v>224.36768702792492</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.2630418889635742</v>
+        <v>-7.2036389771676417</v>
       </c>
       <c r="B50">
-        <v>-4.52546760222041</v>
+        <v>-4.5761465954583924</v>
       </c>
       <c r="C50">
         <v>224.36768702792492</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.0039905725181466</v>
+        <v>-6.9407917925743012</v>
       </c>
       <c r="B51">
-        <v>-4.0033154322569162</v>
+        <v>-4.0570539014191676</v>
       </c>
       <c r="C51">
         <v>224.36768702792492</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.7359795354529526</v>
+        <v>-6.6691644022315986</v>
       </c>
       <c r="B52">
-        <v>-3.4879094183282913</v>
+        <v>-3.5445504808330024</v>
       </c>
       <c r="C52">
         <v>224.36768702792492</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.4594338184276889</v>
+        <v>-6.3892429911173911</v>
       </c>
       <c r="B53">
-        <v>-2.9789295291820963</v>
+        <v>-3.0382714668779509</v>
       </c>
       <c r="C53">
         <v>224.36768702792492</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.1747784621020534</v>
+        <v>-6.1015137442095266</v>
       </c>
       <c r="B54">
-        <v>-2.4760557335658846</v>
+        <v>-2.5378519927320577</v>
       </c>
       <c r="C54">
         <v>224.36768702792492</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.8823570034343922</v>
+        <v>-5.8063667019190461</v>
       </c>
       <c r="B55">
-        <v>-1.9790293678423454</v>
+        <v>-2.0429993451036892</v>
       </c>
       <c r="C55">
         <v>224.36768702792492</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.5821869645776845</v>
+        <v>-5.5038073263897482</v>
       </c>
       <c r="B56">
-        <v>-1.4878372388347003</v>
+        <v>-1.5537094248224952</v>
       </c>
       <c r="C56">
         <v>224.36768702792492</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.2742043639835634</v>
+        <v>-5.1937449351986169</v>
       </c>
       <c r="B57">
-        <v>-1.0025275209813036</v>
+        <v>-1.0700502862484407</v>
       </c>
       <c r="C57">
         <v>224.36768702792492</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.9583452201036584</v>
+        <v>-4.8760888459226388</v>
       </c>
       <c r="B58">
-        <v>-0.52314838872050651</v>
+        <v>-0.59208998374149113</v>
       </c>
       <c r="C58">
         <v>224.36768702792492</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.634553804305555</v>
+        <v>-4.5507598409469283</v>
       </c>
       <c r="B59">
-        <v>-0.049741802518019768</v>
+        <v>-0.11988796767691294</v>
       </c>
       <c r="C59">
         <v>224.36768702792492</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.3028073996206642</v>
+        <v>-4.2177245618891472</v>
       </c>
       <c r="B60">
-        <v>0.41767513305099424</v>
+        <v>0.3465307275088</v>
       </c>
       <c r="C60">
         <v>224.36768702792492</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.9630915419963473</v>
+        <v>-3.8769611151750856</v>
       </c>
       <c r="B61">
-        <v>0.87909152738401453</v>
+        <v>0.80714967136385385</v>
       </c>
       <c r="C61">
         <v>224.36768702792492</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.6153917673799714</v>
+        <v>-3.528447607230536</v>
       </c>
       <c r="B62">
-        <v>1.3344964898785163</v>
+        <v>1.2619524334364503</v>
       </c>
       <c r="C62">
         <v>224.36768702792492</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.2597832814154057</v>
+        <v>-3.1722714139393178</v>
       </c>
       <c r="B63">
-        <v>1.7839466460733764</v>
+        <v>1.7110045866309309</v>
       </c>
       <c r="C63">
         <v>224.36768702792492</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.8966999685325447</v>
+        <v>-2.808956989017354</v>
       </c>
       <c r="B64">
-        <v>2.2277686860730492</v>
+        <v>2.1546997172761744</v>
       </c>
       <c r="C64">
         <v>224.36768702792492</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.5266653828577912</v>
+        <v>-2.4391380556385953</v>
       </c>
       <c r="B65">
-        <v>2.6663568161233884</v>
+        <v>2.5935134150571959</v>
       </c>
       <c r="C65">
         <v>224.36768702792492</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.1502030785175466</v>
+        <v>-2.0634483369769923</v>
       </c>
       <c r="B66">
-        <v>3.1001052424702467</v>
+        <v>3.027921269659009</v>
       </c>
       <c r="C66">
         <v>224.36768702792492</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.7671236113360416</v>
+        <v>-1.6816662173217558</v>
       </c>
       <c r="B67">
-        <v>3.5288713245086485</v>
+        <v>3.4577569653298492</v>
       </c>
       <c r="C67">
         <v>224.36768702792492</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.3743855439288322</v>
+        <v>-1.290148725423149</v>
       </c>
       <c r="B68">
-        <v>3.9503650342302938</v>
+        <v>3.8802865645708176</v>
       </c>
       <c r="C68">
         <v>224.36768702792492</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.96961132973358966</v>
+        <v>-0.88605240680189834</v>
       </c>
       <c r="B69">
-        <v>4.362796215360202</v>
+        <v>4.2933761425457524</v>
       </c>
       <c r="C69">
         <v>224.36768702792492</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.55593097868515773</v>
+        <v>-0.47315322959957118</v>
       </c>
       <c r="B70">
-        <v>4.7685215859599257</v>
+        <v>4.6998594468164985</v>
       </c>
       <c r="C70">
         <v>224.36768702792492</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.13675619613067466</v>
+        <v>-0.055567173652436908</v>
       </c>
       <c r="B71">
-        <v>5.1701099645890594</v>
+        <v>5.1028253932288488</v>
       </c>
       <c r="C71">
         <v>224.36768702792492</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.2888820874306689</v>
+        <v>0.36784915704523657</v>
       </c>
       <c r="B72">
-        <v>5.5668316974627885</v>
+        <v>5.50141589836631</v>
       </c>
       <c r="C72">
         <v>224.36768702792492</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.72254294019699061</v>
+        <v>0.798946062432119</v>
       </c>
       <c r="B73">
-        <v>5.9575128955973051</v>
+        <v>5.8942423692261521</v>
       </c>
       <c r="C73">
         <v>224.36768702792492</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.1637646503076708</v>
+        <v>1.2371420823366255</v>
       </c>
       <c r="B74">
-        <v>6.3425012015572717</v>
+        <v>6.2817411737229811</v>
       </c>
       <c r="C74">
         <v>224.36768702792492</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.6115747068774153</v>
+        <v>1.6812399668491447</v>
       </c>
       <c r="B75">
-        <v>6.7225288602927522</v>
+        <v>6.6648108109661859</v>
       </c>
       <c r="C75">
         <v>224.36768702792492</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.0649781829809681</v>
+        <v>2.1300110672182004</v>
       </c>
       <c r="B76">
-        <v>7.098344994746963</v>
+        <v>7.0443733439269973</v>
       </c>
       <c r="C76">
         <v>224.36768702792492</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.52307846291979</v>
+        <v>2.582342372674137</v>
       </c>
       <c r="B77">
-        <v>7.4706247051448242</v>
+        <v>7.4212640528399332</v>
       </c>
       <c r="C77">
         <v>224.36768702792492</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.9853945919421818</v>
+        <v>3.0376148232164555</v>
       </c>
       <c r="B78">
-        <v>7.8397301228449336</v>
+        <v>7.7959475231308444</v>
       </c>
       <c r="C78">
         <v>224.36768702792492</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.4509756663500588</v>
+        <v>3.4946421435074533</v>
       </c>
       <c r="B79">
-        <v>8.20637722382396</v>
+        <v>8.16931401783159</v>
       </c>
       <c r="C79">
         <v>224.36768702792492</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.9180174839963935</v>
+        <v>3.9512072580557236</v>
       </c>
       <c r="B80">
-        <v>8.5719244688775955</v>
+        <v>8.54302738367834</v>
       </c>
       <c r="C80">
         <v>224.36768702792492</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.3817561562516616</v>
+        <v>4.401532446559691</v>
       </c>
       <c r="B81">
-        <v>8.9399587930668023</v>
+        <v>8.9214236214538882</v>
       </c>
       <c r="C81">
         <v>224.36768702792492</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.7518629331670637</v>
+        <v>4.7370345459494159</v>
       </c>
       <c r="B82">
-        <v>9.3784925672511026</v>
+        <v>9.3859910441078682</v>
       </c>
       <c r="C82">
         <v>224.36768702792492</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.8131831559718465</v>
+        <v>4.806878372189515</v>
       </c>
       <c r="B1">
-        <v>10.332617199358296</v>
+        <v>10.335551779967172</v>
       </c>
       <c r="C1">
         <v>250.99764529992115</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3.979691388933202</v>
+        <v>3.8980746579837797</v>
       </c>
       <c r="B2">
-        <v>10.156961767697425</v>
+        <v>10.212028988817716</v>
       </c>
       <c r="C2">
         <v>250.99764529992115</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.32293232166642</v>
+        <v>3.2129612156972756</v>
       </c>
       <c r="B3">
-        <v>9.8577900800430029</v>
+        <v>9.93237493156983</v>
       </c>
       <c r="C3">
         <v>250.99764529992115</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.7013908894967</v>
+        <v>2.5696031659291512</v>
       </c>
       <c r="B4">
-        <v>9.53400523116968</v>
+        <v>9.6235764584991319</v>
       </c>
       <c r="C4">
         <v>250.99764529992115</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.1069348392137077</v>
+        <v>1.957622595001836</v>
       </c>
       <c r="B5">
-        <v>9.1912907503316852</v>
+        <v>9.29287714255154</v>
       </c>
       <c r="C5">
         <v>250.99764529992115</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.536105658115996</v>
+        <v>1.3726460445710433</v>
       </c>
       <c r="B6">
-        <v>8.8320637484583528</v>
+        <v>8.9433295688156438</v>
       </c>
       <c r="C6">
         <v>250.99764529992115</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>0.98684764217479892</v>
+        <v>0.81209597552024848</v>
       </c>
       <c r="B7">
-        <v>8.4577609311813564</v>
+        <v>8.5767328072385958</v>
       </c>
       <c r="C7">
         <v>250.99764529992115</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.45787129110056496</v>
+        <v>0.2743764596808535</v>
       </c>
       <c r="B8">
-        <v>8.0692835139977372</v>
+        <v>8.19420078326484</v>
       </c>
       <c r="C8">
         <v>250.99764529992115</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-0.052689505369140494</v>
+        <v>-0.24285830661252389</v>
       </c>
       <c r="B9">
-        <v>7.66793569784589</v>
+        <v>7.7973708202037608</v>
       </c>
       <c r="C9">
         <v>250.99764529992115</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.54682166836015955</v>
+        <v>-0.74211326463812477</v>
       </c>
       <c r="B10">
-        <v>7.2551061168537112</v>
+        <v>7.387991316186028</v>
       </c>
       <c r="C10">
         <v>250.99764529992115</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-1.0264187524790776</v>
+        <v>-1.2257800306288147</v>
       </c>
       <c r="B11">
-        <v>6.8321181524657568</v>
+        <v>6.9677315707625587</v>
       </c>
       <c r="C11">
         <v>250.99764529992115</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.4925509706328641</v>
+        <v>-1.6951943764526705</v>
       </c>
       <c r="B12">
-        <v>6.3997197629916975</v>
+        <v>6.5375239255644466</v>
       </c>
       <c r="C12">
         <v>250.99764529992115</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.9430885354492828</v>
+        <v>-2.1475820215639376</v>
       </c>
       <c r="B13">
-        <v>5.9564224668849919</v>
+        <v>6.095431989123238</v>
       </c>
       <c r="C13">
         <v>250.99764529992115</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.3767955122575475</v>
+        <v>-2.58132135966878</v>
       </c>
       <c r="B14">
-        <v>5.5013624849843143</v>
+        <v>5.6403239131846616</v>
       </c>
       <c r="C14">
         <v>250.99764529992115</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.799211377471901</v>
+        <v>-3.0035115338948457</v>
       </c>
       <c r="B15">
-        <v>5.0384112875254177</v>
+        <v>5.1771547554507036</v>
       </c>
       <c r="C15">
         <v>250.99764529992115</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.2154160673820589</v>
+        <v>-3.4206629991343922</v>
       </c>
       <c r="B16">
-        <v>4.5711191779439568</v>
+        <v>4.7104686811927658</v>
       </c>
       <c r="C16">
         <v>250.99764529992115</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.6218759466946224</v>
+        <v>-3.8282107079166221</v>
       </c>
       <c r="B17">
-        <v>4.0970165430780661</v>
+        <v>4.2370793800036006</v>
       </c>
       <c r="C17">
         <v>250.99764529992115</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.0139980877943611</v>
+        <v>-4.2202299883683736</v>
       </c>
       <c r="B18">
-        <v>3.6128934437155111</v>
+        <v>3.7528515512604459</v>
       </c>
       <c r="C18">
         <v>250.99764529992115</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.3915659653618571</v>
+        <v>-4.5964331733700847</v>
       </c>
       <c r="B19">
-        <v>3.1185985530400511</v>
+        <v>3.2575844091570767</v>
       </c>
       <c r="C19">
         <v>250.99764529992115</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.7554571546516557</v>
+        <v>-4.957941846990602</v>
       </c>
       <c r="B20">
-        <v>2.6147451973344444</v>
+        <v>2.7520607965914037</v>
       </c>
       <c r="C20">
         <v>250.99764529992115</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-5.1065492309182865</v>
+        <v>-5.3058775932987627</v>
       </c>
       <c r="B21">
-        <v>2.1019467028814511</v>
+        <v>2.2370635564613424</v>
       </c>
       <c r="C21">
         <v>250.99764529992115</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.4455598655456052</v>
+        <v>-5.6411586710065764</v>
       </c>
       <c r="B22">
-        <v>1.5807046411643413</v>
+        <v>1.7132336146957692</v>
       </c>
       <c r="C22">
         <v>250.99764529992115</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.77256711443472</v>
+        <v>-5.9638900373986932</v>
       </c>
       <c r="B23">
-        <v>1.051073564468433</v>
+        <v>1.1806442293474329</v>
       </c>
       <c r="C23">
         <v>250.99764529992115</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.0874891296160465</v>
+        <v>-6.2739733244029283</v>
       </c>
       <c r="B24">
-        <v>0.51299627027955563</v>
+        <v>0.63922674150004677</v>
       </c>
       <c r="C24">
         <v>250.99764529992115</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.3902440631200079</v>
+        <v>-6.5713101639471008</v>
       </c>
       <c r="B25">
-        <v>-0.033584443916462745</v>
+        <v>0.088912492237326</v>
       </c>
       <c r="C25">
         <v>250.99764529992115</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.6807168680155211</v>
+        <v>-6.8557618533312423</v>
       </c>
       <c r="B26">
-        <v>-0.58874898296947886</v>
+        <v>-0.47039533010790952</v>
       </c>
       <c r="C26">
         <v>250.99764529992115</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.9586597015255141</v>
+        <v>-7.12702835134426</v>
       </c>
       <c r="B27">
-        <v>-1.152670561072116</v>
+        <v>-1.0389061482064368</v>
       </c>
       <c r="C27">
         <v>250.99764529992115</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.2237915219113953</v>
+        <v>-7.3847692821472677</v>
       </c>
       <c r="B28">
-        <v>-1.7255455947526743</v>
+        <v>-1.6168575374799119</v>
       </c>
       <c r="C28">
         <v>250.99764529992115</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.4758312874345929</v>
+        <v>-7.62864426990139</v>
       </c>
       <c r="B29">
-        <v>-2.3075705005394656</v>
+        <v>-2.2044870733500082</v>
       </c>
       <c r="C29">
         <v>250.99764529992115</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.714601654110961</v>
+        <v>-7.85844902692213</v>
       </c>
       <c r="B30">
-        <v>-2.8988692219074155</v>
+        <v>-2.8019373444709084</v>
       </c>
       <c r="C30">
         <v>250.99764529992115</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.9403400689741259</v>
+        <v>-8.07452361814254</v>
       </c>
       <c r="B31">
-        <v>-3.4992758101179668</v>
+        <v>-3.4089709924269025</v>
       </c>
       <c r="C31">
         <v>250.99764529992115</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.1533876768121445</v>
+        <v>-8.2773441966500609</v>
       </c>
       <c r="B32">
-        <v>-4.1085518433791854</v>
+        <v>-4.0252556720348034</v>
       </c>
       <c r="C32">
         <v>250.99764529992115</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.3540856224130842</v>
+        <v>-8.4673869155321331</v>
       </c>
       <c r="B33">
-        <v>-4.7264588998991393</v>
+        <v>-4.650459038111423</v>
       </c>
       <c r="C33">
         <v>250.99764529992115</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.542580047129249</v>
+        <v>-8.644880646609014</v>
       </c>
       <c r="B34">
-        <v>-5.3528948433289338</v>
+        <v>-5.2844213427751665</v>
       </c>
       <c r="C34">
         <v>250.99764529992115</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.7182370785699685</v>
+        <v>-8.8090651366322454</v>
       </c>
       <c r="B35">
-        <v>-5.9883026790918823</v>
+        <v>-5.927673227350847</v>
       </c>
       <c r="C35">
         <v>250.99764529992115</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.8802278409088142</v>
+        <v>-8.9589328510861854</v>
       </c>
       <c r="B36">
-        <v>-6.6332616980543273</v>
+        <v>-6.5809179304648584</v>
       </c>
       <c r="C36">
         <v>250.99764529992115</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-9.0277234583193664</v>
+        <v>-9.0934762554552</v>
       </c>
       <c r="B37">
-        <v>-7.2883511910826329</v>
+        <v>-7.2448586907436159</v>
       </c>
       <c r="C37">
         <v>250.99764529992115</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.1594325910280823</v>
+        <v>-9.2110971070328027</v>
       </c>
       <c r="B38">
-        <v>-7.9544736592659957</v>
+        <v>-7.9206110491319874</v>
       </c>
       <c r="C38">
         <v>250.99764529992115</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.2722140434729869</v>
+        <v>-9.3078343303491113</v>
       </c>
       <c r="B39">
-        <v>-8.6338244445850538</v>
+        <v>-8.6109397558487419</v>
       </c>
       <c r="C39">
         <v>250.99764529992115</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.36246415614498</v>
+        <v>-9.3791361417434018</v>
       </c>
       <c r="B40">
-        <v>-9.3289220992432931</v>
+        <v>-9.3190218634311055</v>
       </c>
       <c r="C40">
         <v>250.99764529992115</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.4265792695349724</v>
+        <v>-9.4204507575549439</v>
       </c>
       <c r="B41">
-        <v>-10.0422851754442</v>
+        <v>-10.048034424416315</v>
       </c>
       <c r="C41">
         <v>250.99764529992115</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.4265792695349724</v>
+        <v>-9.4204507575549439</v>
       </c>
       <c r="B42">
-        <v>-10.0422851754442</v>
+        <v>-10.048034424416315</v>
       </c>
       <c r="C42">
         <v>250.99764529992115</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.2059739925996471</v>
+        <v>-9.177848750304813</v>
       </c>
       <c r="B43">
-        <v>-9.4382911018437667</v>
+        <v>-9.45951637401181</v>
       </c>
       <c r="C43">
         <v>250.99764529992115</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.98610966432601</v>
+        <v>-8.9398290650151733</v>
       </c>
       <c r="B44">
-        <v>-8.8337791885640211</v>
+        <v>-8.8677999559571479</v>
       </c>
       <c r="C44">
         <v>250.99764529992115</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.7639666492400146</v>
+        <v>-8.7024241909727138</v>
       </c>
       <c r="B45">
-        <v>-8.2308598207725</v>
+        <v>-8.27565441214028</v>
       </c>
       <c r="C45">
         <v>250.99764529992115</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.5365253118676261</v>
+        <v>-8.4616666174641324</v>
       </c>
       <c r="B46">
-        <v>-7.63164338363675</v>
+        <v>-7.6858489844491755</v>
       </c>
       <c r="C46">
         <v>250.99764529992115</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.3011995009164448</v>
+        <v>-8.2141505498502543</v>
       </c>
       <c r="B47">
-        <v>-7.0379373056942311</v>
+        <v>-7.1007608483618743</v>
       </c>
       <c r="C47">
         <v>250.99764529992115</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.0571370018206458</v>
+        <v>-7.9587170577884727</v>
       </c>
       <c r="B48">
-        <v>-6.4503371889620649</v>
+        <v>-6.5211989137167992</v>
       </c>
       <c r="C48">
         <v>250.99764529992115</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.8039190841960453</v>
+        <v>-7.6947689270102995</v>
       </c>
       <c r="B49">
-        <v>-5.8691356788272628</v>
+        <v>-5.9475800239424412</v>
       </c>
       <c r="C49">
         <v>250.99764529992115</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.5411270176584635</v>
+        <v>-7.4217089432472605</v>
       </c>
       <c r="B50">
-        <v>-5.29462542067686</v>
+        <v>-5.3803210224673137</v>
       </c>
       <c r="C50">
         <v>250.99764529992115</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.2685122757794272</v>
+        <v>-7.1391623634484267</v>
       </c>
       <c r="B51">
-        <v>-4.7269801064988073</v>
+        <v>-4.8196834723290021</v>
       </c>
       <c r="C51">
         <v>250.99764529992115</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.9865071479533265</v>
+        <v>-6.8476443294330727</v>
       </c>
       <c r="B52">
-        <v>-4.1658976146847762</v>
+        <v>-4.2653078150014618</v>
       </c>
       <c r="C52">
         <v>250.99764529992115</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.6957141275302519</v>
+        <v>-6.5478924542380232</v>
       </c>
       <c r="B53">
-        <v>-3.6109568702273607</v>
+        <v>-3.7166792115677239</v>
       </c>
       <c r="C53">
         <v>250.99764529992115</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.3967357078603033</v>
+        <v>-6.2406443509001006</v>
       </c>
       <c r="B54">
-        <v>-3.0617367981191577</v>
+        <v>-3.173282823110827</v>
       </c>
       <c r="C54">
         <v>250.99764529992115</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.0900517530829825</v>
+        <v>-5.926482604776961</v>
       </c>
       <c r="B55">
-        <v>-2.5179020273621884</v>
+        <v>-2.634712016884869</v>
       </c>
       <c r="C55">
         <v>250.99764529992115</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.77565161049543</v>
+        <v>-5.60536969050959</v>
       </c>
       <c r="B56">
-        <v>-1.9794600029962042</v>
+        <v>-2.1009929848282174</v>
       </c>
       <c r="C56">
         <v>250.99764529992115</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.4534019981841828</v>
+        <v>-5.277113055059802</v>
       </c>
       <c r="B57">
-        <v>-1.4465038740703742</v>
+        <v>-1.5722601250502908</v>
       </c>
       <c r="C57">
         <v>250.99764529992115</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.1231696342357909</v>
+        <v>-4.9415201453894158</v>
       </c>
       <c r="B58">
-        <v>-0.919126789633881</v>
+        <v>-1.048647835660522</v>
       </c>
       <c r="C58">
         <v>250.99764529992115</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.7848378671555674</v>
+        <v>-4.5984221674837489</v>
       </c>
       <c r="B59">
-        <v>-0.39741027594585077</v>
+        <v>-0.53027393145252621</v>
       </c>
       <c r="C59">
         <v>250.99764529992115</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.4383565671239342</v>
+        <v>-4.2477453634221591</v>
       </c>
       <c r="B60">
-        <v>0.11861063189474086</v>
+        <v>-0.017189893956711094</v>
       </c>
       <c r="C60">
         <v>250.99764529992115</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.0836922347400861</v>
+        <v>-3.8894397343075076</v>
       </c>
       <c r="B61">
-        <v>0.628912521578962</v>
+        <v>0.49056937861232114</v>
       </c>
       <c r="C61">
         <v>250.99764529992115</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.7208113706032186</v>
+        <v>-3.5234552812426547</v>
       </c>
       <c r="B62">
-        <v>1.133471980797881</v>
+        <v>0.99296898803996814</v>
       </c>
       <c r="C62">
         <v>250.99764529992115</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.3498239154992331</v>
+        <v>-3.1499288599864572</v>
       </c>
       <c r="B63">
-        <v>1.6323658457808574</v>
+        <v>1.4901044568660322</v>
       </c>
       <c r="C63">
         <v>250.99764529992115</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.9714135709608338</v>
+        <v>-2.7697447449217472</v>
       </c>
       <c r="B64">
-        <v>2.1260719469104217</v>
+        <v>1.98259299064794</v>
       </c>
       <c r="C64">
         <v>250.99764529992115</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.5864074787074358</v>
+        <v>-2.3839740650873553</v>
       </c>
       <c r="B65">
-        <v>2.615168363107391</v>
+        <v>2.4711822156975187</v>
       </c>
       <c r="C65">
         <v>250.99764529992115</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.1956327804584475</v>
+        <v>-1.9936879495221085</v>
       </c>
       <c r="B66">
-        <v>3.1002331732925885</v>
+        <v>2.9566197583266005</v>
       </c>
       <c r="C66">
         <v>250.99764529992115</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.7988088667973066</v>
+        <v>-1.5985346196965125</v>
       </c>
       <c r="B67">
-        <v>3.5810702630821156</v>
+        <v>3.4386600842670854</v>
       </c>
       <c r="C67">
         <v>250.99764529992115</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.3912241237635497</v>
+        <v>-1.1924706668077811</v>
       </c>
       <c r="B68">
-        <v>4.0543867448731952</v>
+        <v>3.9130850169311677</v>
       </c>
       <c r="C68">
         <v>250.99764529992115</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.96920591504170162</v>
+        <v>-0.770791983120492</v>
       </c>
       <c r="B69">
-        <v>4.51761585944188</v>
+        <v>4.3766111846715567</v>
       </c>
       <c r="C69">
         <v>250.99764529992115</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.53766851944015648</v>
+        <v>-0.33984329544198405</v>
       </c>
       <c r="B70">
-        <v>4.9741921342983835</v>
+        <v>4.8336670779227218</v>
       </c>
       <c r="C70">
         <v>250.99764529992115</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.1019689568652611</v>
+        <v>0.093458787371364108</v>
       </c>
       <c r="B71">
-        <v>5.427859523125127</v>
+        <v>5.2890803491730285</v>
       </c>
       <c r="C71">
         <v>250.99764529992115</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.33935170350868304</v>
+        <v>0.5309589628097714</v>
       </c>
       <c r="B72">
-        <v>5.8775983975591846</v>
+        <v>5.7415634370446629</v>
       </c>
       <c r="C72">
         <v>250.99764529992115</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.78866685321753738</v>
+        <v>0.9756752194072611</v>
       </c>
       <c r="B73">
-        <v>6.3217500241749063</v>
+        <v>6.1890098468436614</v>
       </c>
       <c r="C73">
         <v>250.99764529992115</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.2451917759057785</v>
+        <v>1.4265574035264832</v>
       </c>
       <c r="B74">
-        <v>6.7608628313411057</v>
+        <v>6.63215256447769</v>
       </c>
       <c r="C74">
         <v>250.99764529992115</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.7073407269420793</v>
+        <v>1.8815218400991354</v>
       </c>
       <c r="B75">
-        <v>7.196045075990857</v>
+        <v>7.0724459528198409</v>
       </c>
       <c r="C75">
         <v>250.99764529992115</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.1734819564832972</v>
+        <v>2.3384189105044846</v>
       </c>
       <c r="B76">
-        <v>7.6284371675198379</v>
+        <v>7.51139040200333</v>
       </c>
       <c r="C76">
         <v>250.99764529992115</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.642130716497598</v>
+        <v>2.7952843358451975</v>
       </c>
       <c r="B77">
-        <v>8.0590767776108887</v>
+        <v>7.950356938799148</v>
       </c>
       <c r="C77">
         <v>250.99764529992115</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.112436271410211</v>
+        <v>3.2509611396699674</v>
       </c>
       <c r="B78">
-        <v>8.4885584746329243</v>
+        <v>8.3901531092692547</v>
       </c>
       <c r="C78">
         <v>250.99764529992115</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.582809166230656</v>
+        <v>3.7033382306169611</v>
       </c>
       <c r="B79">
-        <v>8.9179931086422535</v>
+        <v>8.8322524123027453</v>
       </c>
       <c r="C79">
         <v>250.99764529992115</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.0503163364468691</v>
+        <v>4.1485678224784781</v>
       </c>
       <c r="B80">
-        <v>9.34943056145241</v>
+        <v>9.279340524514561</v>
       </c>
       <c r="C80">
         <v>250.99764529992115</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.5074013604405865</v>
+        <v>4.576848078589749</v>
       </c>
       <c r="B81">
-        <v>9.788151920876798</v>
+        <v>9.7382589287972259</v>
       </c>
       <c r="C81">
         <v>250.99764529992115</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.8131831559718465</v>
+        <v>4.806878372189515</v>
       </c>
       <c r="B82">
-        <v>10.332617199358296</v>
+        <v>10.335551779967172</v>
       </c>
       <c r="C82">
         <v>250.99764529992115</v>
